--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1295,6 +1295,116 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120248663</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klövsjön 1, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>613897</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6561686</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Wohlgemuth</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120220646</v>
+        <v>120218304</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
+        <v>91335</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120218304</v>
+        <v>120221285</v>
       </c>
       <c r="B3" t="n">
-        <v>91317</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613814</v>
+        <v>613874</v>
       </c>
       <c r="R3" t="n">
-        <v>6561654</v>
+        <v>6561643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120221285</v>
+        <v>120221737</v>
       </c>
       <c r="B4" t="n">
-        <v>78171</v>
+        <v>91335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613874</v>
+        <v>613859</v>
       </c>
       <c r="R4" t="n">
-        <v>6561643</v>
+        <v>6561612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120220387</v>
+        <v>120220646</v>
       </c>
       <c r="B5" t="n">
-        <v>94574</v>
+        <v>4772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,24 +997,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120221614</v>
+        <v>120220387</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>94597</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,39 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613859</v>
+        <v>613814</v>
       </c>
       <c r="R6" t="n">
-        <v>6561612</v>
+        <v>6561654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120221737</v>
+        <v>120221614</v>
       </c>
       <c r="B7" t="n">
-        <v>91317</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,28 +1202,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>366</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
@@ -1300,7 +1300,7 @@
         <v>120248663</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120218304</v>
+        <v>120221614</v>
       </c>
       <c r="B2" t="n">
-        <v>91335</v>
+        <v>5169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613814</v>
+        <v>613859</v>
       </c>
       <c r="R2" t="n">
-        <v>6561654</v>
+        <v>6561612</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120221285</v>
+        <v>120218304</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>91335</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613874</v>
+        <v>613814</v>
       </c>
       <c r="R3" t="n">
-        <v>6561643</v>
+        <v>6561654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120221737</v>
+        <v>120220387</v>
       </c>
       <c r="B4" t="n">
-        <v>91335</v>
+        <v>94597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>366</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613859</v>
+        <v>613814</v>
       </c>
       <c r="R4" t="n">
-        <v>6561612</v>
+        <v>6561654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120220646</v>
+        <v>120221285</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613814</v>
+        <v>613874</v>
       </c>
       <c r="R5" t="n">
-        <v>6561654</v>
+        <v>6561643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120220387</v>
+        <v>120221737</v>
       </c>
       <c r="B6" t="n">
-        <v>94597</v>
+        <v>91335</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613814</v>
+        <v>613859</v>
       </c>
       <c r="R6" t="n">
-        <v>6561654</v>
+        <v>6561612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120221614</v>
+        <v>120220646</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,27 +1206,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613859</v>
+        <v>613814</v>
       </c>
       <c r="R7" t="n">
-        <v>6561612</v>
+        <v>6561654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120221614</v>
+        <v>120221737</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
+        <v>91335</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120220387</v>
+        <v>120221614</v>
       </c>
       <c r="B4" t="n">
-        <v>94597</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613814</v>
+        <v>613859</v>
       </c>
       <c r="R4" t="n">
-        <v>6561654</v>
+        <v>6561612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120221737</v>
+        <v>120220646</v>
       </c>
       <c r="B6" t="n">
-        <v>91335</v>
+        <v>4772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,38 +1100,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>366</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613859</v>
+        <v>613814</v>
       </c>
       <c r="R6" t="n">
-        <v>6561612</v>
+        <v>6561654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120220646</v>
+        <v>120220387</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>94597</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,29 +1211,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120221737</v>
+        <v>120218304</v>
       </c>
       <c r="B2" t="n">
         <v>91335</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613859</v>
+        <v>613814</v>
       </c>
       <c r="R2" t="n">
-        <v>6561612</v>
+        <v>6561654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120218304</v>
+        <v>120220387</v>
       </c>
       <c r="B3" t="n">
-        <v>91335</v>
+        <v>94597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120221614</v>
+        <v>120221285</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>78187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613859</v>
+        <v>613874</v>
       </c>
       <c r="R4" t="n">
-        <v>6561612</v>
+        <v>6561643</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120221285</v>
+        <v>120221614</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613874</v>
+        <v>613859</v>
       </c>
       <c r="R5" t="n">
-        <v>6561643</v>
+        <v>6561612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120220646</v>
+        <v>120221737</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>91335</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,43 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613814</v>
+        <v>613859</v>
       </c>
       <c r="R6" t="n">
-        <v>6561654</v>
+        <v>6561612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120220387</v>
+        <v>120220646</v>
       </c>
       <c r="B7" t="n">
-        <v>94597</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,24 +1206,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120220387</v>
+        <v>120220646</v>
       </c>
       <c r="B3" t="n">
-        <v>94597</v>
+        <v>4772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,24 +793,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120221285</v>
+        <v>120220387</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
+        <v>94597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613874</v>
+        <v>613814</v>
       </c>
       <c r="R4" t="n">
-        <v>6561643</v>
+        <v>6561654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120221614</v>
+        <v>120221285</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613859</v>
+        <v>613874</v>
       </c>
       <c r="R5" t="n">
-        <v>6561612</v>
+        <v>6561643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120221737</v>
+        <v>120221614</v>
       </c>
       <c r="B6" t="n">
-        <v>91335</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,28 +1100,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>366</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120220646</v>
+        <v>120221737</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>91335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,43 +1207,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613814</v>
+        <v>613859</v>
       </c>
       <c r="R7" t="n">
-        <v>6561654</v>
+        <v>6561612</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120218304</v>
+        <v>120221285</v>
       </c>
       <c r="B2" t="n">
-        <v>91335</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613814</v>
+        <v>613874</v>
       </c>
       <c r="R2" t="n">
-        <v>6561654</v>
+        <v>6561643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120220646</v>
+        <v>120221737</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>91335</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613814</v>
+        <v>613859</v>
       </c>
       <c r="R3" t="n">
-        <v>6561654</v>
+        <v>6561612</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120220387</v>
+        <v>120218304</v>
       </c>
       <c r="B4" t="n">
-        <v>94597</v>
+        <v>91335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120221285</v>
+        <v>120221614</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613874</v>
+        <v>613859</v>
       </c>
       <c r="R5" t="n">
-        <v>6561643</v>
+        <v>6561612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120221614</v>
+        <v>120220646</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>4772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,27 +1104,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613859</v>
+        <v>613814</v>
       </c>
       <c r="R6" t="n">
-        <v>6561612</v>
+        <v>6561654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120221737</v>
+        <v>120220387</v>
       </c>
       <c r="B7" t="n">
-        <v>91335</v>
+        <v>94597</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>366</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613859</v>
+        <v>613814</v>
       </c>
       <c r="R7" t="n">
-        <v>6561612</v>
+        <v>6561654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120221285</v>
+        <v>120221614</v>
       </c>
       <c r="B2" t="n">
-        <v>78187</v>
+        <v>5169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613874</v>
+        <v>613859</v>
       </c>
       <c r="R2" t="n">
-        <v>6561643</v>
+        <v>6561612</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120221737</v>
+        <v>120221285</v>
       </c>
       <c r="B3" t="n">
-        <v>91335</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613859</v>
+        <v>613874</v>
       </c>
       <c r="R3" t="n">
-        <v>6561612</v>
+        <v>6561643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120218304</v>
+        <v>120221737</v>
       </c>
       <c r="B4" t="n">
         <v>91335</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613814</v>
+        <v>613859</v>
       </c>
       <c r="R4" t="n">
-        <v>6561654</v>
+        <v>6561612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120221614</v>
+        <v>120220387</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>94597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613859</v>
+        <v>613814</v>
       </c>
       <c r="R5" t="n">
-        <v>6561612</v>
+        <v>6561654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120220646</v>
+        <v>120218304</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>91335</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,33 +1100,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120220387</v>
+        <v>120220646</v>
       </c>
       <c r="B7" t="n">
-        <v>94597</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,24 +1206,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,324 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122747221</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4867</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101675</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Aspvedgnagare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ptilinus fuscus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Geoffroy, 1785)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Krankpunsen V, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>613807</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6561657</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122747223</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92153</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svarttj. SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>613830</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6561610</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122747222</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92153</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Krankpunsen V, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>613863</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6561614</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747222</v>
+        <v>122747221</v>
       </c>
       <c r="B9" t="n">
-        <v>92256</v>
+        <v>4867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613863</v>
+        <v>613807</v>
       </c>
       <c r="R9" t="n">
-        <v>6561614</v>
+        <v>6561657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747221</v>
+        <v>122747223</v>
       </c>
       <c r="B10" t="n">
-        <v>4867</v>
+        <v>92260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,38 +1525,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101675</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613807</v>
+        <v>613830</v>
       </c>
       <c r="R10" t="n">
-        <v>6561657</v>
+        <v>6561610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747223</v>
+        <v>122747222</v>
       </c>
       <c r="B11" t="n">
-        <v>92256</v>
+        <v>92260</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,14 +1655,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613830</v>
+        <v>613863</v>
       </c>
       <c r="R11" t="n">
-        <v>6561610</v>
+        <v>6561614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747221</v>
+        <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>4867</v>
+        <v>92260</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101675</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613807</v>
+        <v>613863</v>
       </c>
       <c r="R9" t="n">
-        <v>6561657</v>
+        <v>6561614</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747223</v>
+        <v>122747221</v>
       </c>
       <c r="B10" t="n">
-        <v>92260</v>
+        <v>4867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,38 +1525,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613830</v>
+        <v>613807</v>
       </c>
       <c r="R10" t="n">
-        <v>6561610</v>
+        <v>6561657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747222</v>
+        <v>122747223</v>
       </c>
       <c r="B11" t="n">
         <v>92260</v>
@@ -1655,14 +1655,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613863</v>
+        <v>613830</v>
       </c>
       <c r="R11" t="n">
-        <v>6561614</v>
+        <v>6561610</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747221</v>
+        <v>122747223</v>
       </c>
       <c r="B10" t="n">
-        <v>4867</v>
+        <v>92260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,38 +1525,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101675</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613807</v>
+        <v>613830</v>
       </c>
       <c r="R10" t="n">
-        <v>6561657</v>
+        <v>6561610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747223</v>
+        <v>122747221</v>
       </c>
       <c r="B11" t="n">
-        <v>92260</v>
+        <v>4867</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,38 +1631,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613830</v>
+        <v>613807</v>
       </c>
       <c r="R11" t="n">
-        <v>6561610</v>
+        <v>6561657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747223</v>
+        <v>122747221</v>
       </c>
       <c r="B10" t="n">
-        <v>92260</v>
+        <v>4867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,38 +1525,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613830</v>
+        <v>613807</v>
       </c>
       <c r="R10" t="n">
-        <v>6561610</v>
+        <v>6561657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747221</v>
+        <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>4867</v>
+        <v>92260</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,38 +1631,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101675</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613807</v>
+        <v>613830</v>
       </c>
       <c r="R11" t="n">
-        <v>6561657</v>
+        <v>6561610</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747222</v>
+        <v>122747221</v>
       </c>
       <c r="B9" t="n">
-        <v>92260</v>
+        <v>4867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613863</v>
+        <v>613807</v>
       </c>
       <c r="R9" t="n">
-        <v>6561614</v>
+        <v>6561657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747221</v>
+        <v>122747222</v>
       </c>
       <c r="B10" t="n">
-        <v>4867</v>
+        <v>92260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,25 +1525,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101675</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613807</v>
+        <v>613863</v>
       </c>
       <c r="R10" t="n">
-        <v>6561657</v>
+        <v>6561614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747221</v>
+        <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>4867</v>
+        <v>92268</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101675</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613807</v>
+        <v>613863</v>
       </c>
       <c r="R9" t="n">
-        <v>6561657</v>
+        <v>6561614</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747222</v>
+        <v>122747221</v>
       </c>
       <c r="B10" t="n">
-        <v>92260</v>
+        <v>4867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,25 +1525,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613863</v>
+        <v>613807</v>
       </c>
       <c r="R10" t="n">
-        <v>6561614</v>
+        <v>6561657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
         <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>92260</v>
+        <v>92268</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747222</v>
+        <v>122747223</v>
       </c>
       <c r="B9" t="n">
         <v>92268</v>
@@ -1443,14 +1443,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613863</v>
+        <v>613830</v>
       </c>
       <c r="R9" t="n">
-        <v>6561614</v>
+        <v>6561610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747223</v>
+        <v>122747222</v>
       </c>
       <c r="B11" t="n">
         <v>92268</v>
@@ -1655,14 +1655,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613830</v>
+        <v>613863</v>
       </c>
       <c r="R11" t="n">
-        <v>6561610</v>
+        <v>6561614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747223</v>
+        <v>122747221</v>
       </c>
       <c r="B9" t="n">
-        <v>92268</v>
+        <v>4867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,38 +1419,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613830</v>
+        <v>613807</v>
       </c>
       <c r="R9" t="n">
-        <v>6561610</v>
+        <v>6561657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747221</v>
+        <v>122747222</v>
       </c>
       <c r="B10" t="n">
-        <v>4867</v>
+        <v>92268</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,25 +1525,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101675</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613807</v>
+        <v>613863</v>
       </c>
       <c r="R10" t="n">
-        <v>6561657</v>
+        <v>6561614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747222</v>
+        <v>122747223</v>
       </c>
       <c r="B11" t="n">
         <v>92268</v>
@@ -1655,14 +1655,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613863</v>
+        <v>613830</v>
       </c>
       <c r="R11" t="n">
-        <v>6561614</v>
+        <v>6561610</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747221</v>
+        <v>122747223</v>
       </c>
       <c r="B9" t="n">
-        <v>4867</v>
+        <v>92268</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,38 +1419,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101675</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613807</v>
+        <v>613830</v>
       </c>
       <c r="R9" t="n">
-        <v>6561657</v>
+        <v>6561610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747222</v>
+        <v>122747221</v>
       </c>
       <c r="B10" t="n">
-        <v>92268</v>
+        <v>4867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,25 +1525,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613863</v>
+        <v>613807</v>
       </c>
       <c r="R10" t="n">
-        <v>6561614</v>
+        <v>6561657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747223</v>
+        <v>122747222</v>
       </c>
       <c r="B11" t="n">
         <v>92268</v>
@@ -1655,14 +1655,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613830</v>
+        <v>613863</v>
       </c>
       <c r="R11" t="n">
-        <v>6561610</v>
+        <v>6561614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747223</v>
+        <v>122747221</v>
       </c>
       <c r="B9" t="n">
-        <v>92268</v>
+        <v>4867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,38 +1419,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613830</v>
+        <v>613807</v>
       </c>
       <c r="R9" t="n">
-        <v>6561610</v>
+        <v>6561657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747221</v>
+        <v>122747223</v>
       </c>
       <c r="B10" t="n">
-        <v>4867</v>
+        <v>92271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,38 +1525,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101675</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613807</v>
+        <v>613830</v>
       </c>
       <c r="R10" t="n">
-        <v>6561657</v>
+        <v>6561610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
         <v>122747222</v>
       </c>
       <c r="B11" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747221</v>
+        <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>4867</v>
+        <v>92273</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101675</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613807</v>
+        <v>613863</v>
       </c>
       <c r="R9" t="n">
-        <v>6561657</v>
+        <v>6561614</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747223</v>
+        <v>122747221</v>
       </c>
       <c r="B10" t="n">
-        <v>92271</v>
+        <v>4867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,38 +1525,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613830</v>
+        <v>613807</v>
       </c>
       <c r="R10" t="n">
-        <v>6561610</v>
+        <v>6561657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747222</v>
+        <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>92271</v>
+        <v>92273</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,14 +1655,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613863</v>
+        <v>613830</v>
       </c>
       <c r="R11" t="n">
-        <v>6561614</v>
+        <v>6561610</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>93218</v>
+        <v>93224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>93218</v>
+        <v>93224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>93224</v>
+        <v>93234</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>93224</v>
+        <v>93234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>93234</v>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>93234</v>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>93235</v>
+        <v>93236</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>93235</v>
+        <v>93236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>93236</v>
+        <v>93238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>93236</v>
+        <v>93238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>93238</v>
+        <v>93239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>93238</v>
+        <v>93239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>93239</v>
+        <v>93242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>93239</v>
+        <v>93242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -1410,7 +1410,7 @@
         <v>122747222</v>
       </c>
       <c r="B9" t="n">
-        <v>93242</v>
+        <v>93243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>122747223</v>
       </c>
       <c r="B11" t="n">
-        <v>93242</v>
+        <v>93243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120220646</v>
+        <v>120221285</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613814</v>
+        <v>613874</v>
       </c>
       <c r="R2" t="n">
-        <v>6561654</v>
+        <v>6561643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,12 +775,7 @@
         <v>120218304</v>
       </c>
       <c r="B3" t="n">
-        <v>91335</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120221285</v>
+        <v>120221737</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613874</v>
+        <v>613859</v>
       </c>
       <c r="R4" t="n">
-        <v>6561643</v>
+        <v>6561612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,55 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120221614</v>
+        <v>122747224</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klövsjön, Klövsjön, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613859</v>
+        <v>613839</v>
       </c>
       <c r="R5" t="n">
-        <v>6561612</v>
+        <v>6561597</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,49 +1051,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120221737</v>
+        <v>120220387</v>
       </c>
       <c r="B6" t="n">
-        <v>91335</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>366</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613859</v>
+        <v>613814</v>
       </c>
       <c r="R6" t="n">
-        <v>6561612</v>
+        <v>6561654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,53 +1164,55 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120220387</v>
+        <v>120248663</v>
       </c>
       <c r="B7" t="n">
-        <v>94597</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Klövsjön, Klövsjön, Srm</t>
+          <t>Klövsjön 1, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613814</v>
+        <v>613897</v>
       </c>
       <c r="R7" t="n">
-        <v>6561654</v>
+        <v>6561686</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,78 +1250,67 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Daniel Wohlgemuth</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Daniel Wohlgemuth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120248663</v>
+        <v>122747222</v>
       </c>
       <c r="B8" t="n">
-        <v>91906</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Klövsjön 1, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613897</v>
+        <v>613863</v>
       </c>
       <c r="R8" t="n">
-        <v>6561686</v>
+        <v>6561614</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1374,12 +1334,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-11-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,29 +1348,32 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Wohlgemuth</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Wohlgemuth</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747222</v>
+        <v>122747223</v>
       </c>
       <c r="B9" t="n">
-        <v>93243</v>
+        <v>93309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,14 +1401,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Svarttj. SV, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613863</v>
+        <v>613830</v>
       </c>
       <c r="R9" t="n">
-        <v>6561614</v>
+        <v>6561610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747221</v>
+        <v>120221614</v>
       </c>
       <c r="B10" t="n">
-        <v>4872</v>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,34 +1482,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101675</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krankpunsen V, Srm</t>
+          <t>Klövsjön, Klövsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613807</v>
+        <v>613859</v>
       </c>
       <c r="R10" t="n">
-        <v>6561657</v>
+        <v>6561612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,12 +1541,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,61 +1561,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747223</v>
+        <v>122747221</v>
       </c>
       <c r="B11" t="n">
-        <v>93243</v>
+        <v>4873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>101675</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttj. SV, Srm</t>
+          <t>Krankpunsen V, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613830</v>
+        <v>613807</v>
       </c>
       <c r="R11" t="n">
-        <v>6561610</v>
+        <v>6561657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,6 +1671,108 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120220646</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Klövsjön, Klövsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>613814</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6561654</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35182-2024 artfynd.xlsx
+++ b/artfynd/A 35182-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120221285</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120218304</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120221737</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747224</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120220387</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120248663</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747222</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747223</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120221614</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747221</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1773,8 +1828,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120220646</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>